--- a/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
+++ b/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
@@ -498,7 +498,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Do not look at the existing labels while coding: the kinds-of-work rows file in analysis/output, the review table in analysis/, and the task tables in the notebook (parts 5 to 8).</t>
+          <t>Do not look at the existing labels while coding: the kinds-of-work rows file and codebook in docs/measurement (and their older copies in analysis/), and the task, problem and cause tables in parts 5 to 9 of the analysis notebook.</t>
         </is>
       </c>
     </row>

--- a/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
+++ b/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Do not look at the existing labels while coding: the kinds-of-work rows file and codebook in docs/measurement (and their older copies in analysis/), and the task, problem and cause tables in parts 5 to 9 of the analysis notebook.</t>
+          <t>Do not look at the existing labels while coding: the kinds-of-work rows file and codebook in docs/measurement, and the task, problem, candidate and cause tables in parts 5 to 9 of the analysis notebook.</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3. If the note does not say what the work concerned (for example an empty note, '/', or only 'Forward'), leave the kinds empty and put Y in 'No kind: too little detail'. Do not guess a kind from the case alone.</t>
+          <t>3. If the note does not say what the work concerned (an empty note, '/', or only 'Pause for now' or 'Forward'), leave the kinds empty and put Y in 'No kind: too little detail'. Do not guess a kind from the case alone.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4. K01 (receive a request) is added automatically to every REQ record, so do not enter it.</t>
+          <t>4. K01 (receive a request) is added automatically to incoming REQ records, so do not enter it.</t>
         </is>
       </c>
     </row>
@@ -582,6 +582,13 @@
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>When you are done, save the file and send it back. The comparison is then added to the notebook, and disagreements are used to sharpen the definitions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Codebook revised on 6 October 2026; this sheet uses the revised definitions.</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3924,7 +3931,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Intake of a request: every row coded REQ, on all five days, next to any kind its note shows.</t>
+          <t>An incoming request marked REQ, except REQ-Exact, which identifies an earlier-generated PO.</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3943,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Create or complete a PO for a need</t>
+          <t>PO preparation and completion</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Enter or amend PO lines in Exact for a need, including adding lines, ordering via a supplier website and PO paperwork.</t>
+          <t>Broad PO preparation, entry, amendment and supporting paperwork. Includes combined intervals; it does not measure typing time separately.</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3960,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Maximalisatie and HOLD/order decision</t>
+          <t>MAX, demand consolidation and HOLD/order decisions</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3975,7 +3982,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Check price, and ETA where the supplier states it, against a quotation, website or supplier information before the PO is sent.</t>
+          <t>A check before release. Price comparison is explicit in some notes; retain unspecified check fields and types where the note does not establish them.</t>
         </is>
       </c>
     </row>
@@ -4191,12 +4198,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Check a supplier confirmation</t>
+          <t>Monitoring checks and confirmation handling</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>After ordering: compare the confirmation with the PO on price and ETA, update Exact, attach the confirmation.</t>
+          <t>Monitoring-stage CHECK records and related confirmation handling. Some check subtypes are unspecified; attachment is handling, not checking. Do not equate the entire category with price matching.</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4480,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>K01 is automatic for every REQ record; do not enter it.</t>
+          <t>K01 is added automatically to incoming REQ records; do not enter it. REQ-Exact records point to an earlier PO and get no K01.</t>
         </is>
       </c>
       <c r="C36" s="2" t="n"/>
@@ -4486,7 +4493,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Code from the record's note and its case context. If the note does not say what the work concerned, give no kind.</t>
+          <t>Code from the record's note and its case context. Do not guess a kind from the case alone.</t>
         </is>
       </c>
       <c r="C37" s="2" t="n"/>
@@ -4499,7 +4506,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>A note marked [uncertain] gets no kind.</t>
+          <t>No kind when the note is empty or '/', or says only 'Pause for now' or 'Forward': it does not say what the work concerned.</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -4512,10 +4519,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>A note marked [uncertain] gets no kind.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>Former EXC records are coded like any other record.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
+++ b/docs/measurement/Kinds_Coding_Check_Sample_2026-10-02.xlsx
@@ -536,7 +536,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3. If the note does not say what the work concerned (an empty note, '/', or only 'Pause for now' or 'Forward'), leave the kinds empty and put Y in 'No kind: too little detail'. Do not guess a kind from the case alone.</t>
+          <t>3. If the note is empty or '/', or says only 'Pause for now' or 'Forward', use the activity code, the reviewed stage and the other records of the case. Enter kinds only if these show what the work concerned (see rule 4 in the Codebook sheet); otherwise leave the kinds empty and put Y in 'No kind: too little detail'.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Codebook revised on 6 October 2026; this sheet uses the revised definitions.</t>
+          <t>Codebook revised on 6 October 2026; this sheet uses the revised definitions. Rule 4 and step 3 corrected on 6 October to match how the labels treat records with little or no note.</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>No kind when the note is empty or '/', or says only 'Pause for now' or 'Forward': it does not say what the work concerned.</t>
+          <t>When the note is empty or '/', or says only 'Pause for now' or 'Forward', code from the activity code, the reviewed stage and the other records of the case where these show what the work concerned: usually a PO record is K02, a SEND record K05 and a CHECK in Monitoring K17, unless the case shows other work. If they do not show it, give no kind (this happens mostly with CLAR records).</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
